--- a/logs/Consolidado_15_03_2026.xlsx
+++ b/logs/Consolidado_15_03_2026.xlsx
@@ -638,10 +638,10 @@
         <v>151</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -657,10 +657,10 @@
         <v>65</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -676,10 +676,10 @@
         <v>78</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
@@ -714,10 +714,10 @@
         <v>47</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -739,7 +739,7 @@
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -988,40 +988,40 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Antirougeurs DAY Soothing Emulsion
 Emulsão Antivermelhidão Pele Mista SPF30
 40 ml</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/antirougeurs-day-soothing-emulsion-4878505.html</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>4878505</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -1347,40 +1347,40 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>Cicalfate+ Hydrating Skin Repairing Emulsion
 Creme Hidratante Pós-Cirúrgico e Pós-Tatuagem
 40 ml</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/cicalfate-hydrating-skin-repairing-emulsion-7632459.html</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr"/>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>7632459</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -1466,80 +1466,80 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>Cicalfate+ Purifying Cleansing Gel
 Gel de Limpeza Purificante da Pele Irritada
 200 ml</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/cicalfate-purifying-cleansing-gel-7632460.html</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr"/>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>7632460</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Cicalfate+ Repair Lip Blam
 Bálsamo Repara e Protege Lábios Gretados 24H
 12 ml</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/cicalfate-repair-lip-blam-7850120.html</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr"/>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>7850120</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -1632,40 +1632,40 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>Cicalfate+ Scar Gel
 Gel Reduz e Melhora Aspeto das Cicatrizes
 40 ml</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/cicalfate-scar-gel-8726970.html</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>8726970</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -2404,40 +2404,40 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>Cold Cream Nousishing Lip Balm
 Bálsamo Reparador de Lábios Secos
 4gr</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/cold-cream-nousishing-lip-balm-3000767.html</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr"/>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr"/>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>3000767</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -2803,40 +2803,40 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>Couvrance High Definition Mascara Black
 Máscara de Pestanas Alta Definição Preta
 7 ml</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/couvrance-high-definition-mascara-black-8154716.html</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr"/>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr"/>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>8154716</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -2963,40 +2963,40 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>Dermabsolu Concentrated Resculpting Serum
 Sérum Anti Idade Rugas e Firmeza
 30 ml</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/dermabsolu-concentrated-resculpting-serum-6739621.html</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr"/>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr"/>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
         <is>
           <t>6739621</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
+      <c r="H55" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -3083,40 +3083,40 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>Dermabsolu Intensive Resculpting Night Cream
 Creme Noite Anti Idade Rugas e Firmeza
 40 ml</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/dermabsolu-intensive-resculpting-night-cream-8152748.html</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr"/>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr">
+      <c r="E58" s="7" t="inlineStr"/>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
         <is>
           <t>8152748</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
+      <c r="H58" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -3323,40 +3323,40 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>Hyaluron Activ B3 Cell Renewal Aqua Cream-Gel
 Creme-Gel Dia Rugas AH, Niacinamida
 50 ml</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/hyaluron-activ-b3-cell-renewal-aqua-cream-gel-7982205.html</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr"/>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr"/>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
         <is>
           <t>7982205</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
+      <c r="H64" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -4243,40 +4243,40 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="5" t="inlineStr">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C87" s="7" t="inlineStr">
         <is>
           <t>MEN Shaving Foam
 Espuma de Barbear Calmante sem Álcool
 200ml</t>
         </is>
       </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D87" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/men-shaving-foam-3000655.html</t>
         </is>
       </c>
-      <c r="E87" s="5" t="inlineStr"/>
-      <c r="F87" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G87" s="5" t="inlineStr">
+      <c r="E87" s="7" t="inlineStr"/>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
         <is>
           <t>3000655</t>
         </is>
       </c>
-      <c r="H87" s="5" t="inlineStr">
+      <c r="H87" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -4409,40 +4409,40 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="C91" s="7" t="inlineStr">
         <is>
           <t>Milk Cleanser Dry Sensitive Skin
 Leite de Limpeza Desmaquilhante Pele Seca
 200 ml</t>
         </is>
       </c>
-      <c r="D91" s="3" t="inlineStr">
+      <c r="D91" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/milk-cleanser-dry-sensitive-skin-3001085.html</t>
         </is>
       </c>
-      <c r="E91" s="3" t="inlineStr"/>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G91" s="3" t="inlineStr">
+      <c r="E91" s="7" t="inlineStr"/>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
         <is>
           <t>3001085</t>
         </is>
       </c>
-      <c r="H91" s="3" t="inlineStr">
+      <c r="H91" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -4649,40 +4649,40 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="inlineStr">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C97" s="3" t="inlineStr">
+      <c r="C97" s="7" t="inlineStr">
         <is>
           <t>Soothing Toning Lotion
 Tónico Suave Hidratante Rosto e Olhos
 200 ml</t>
         </is>
       </c>
-      <c r="D97" s="3" t="inlineStr">
+      <c r="D97" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/soothing-toning-lotion-3001045.html</t>
         </is>
       </c>
-      <c r="E97" s="3" t="inlineStr"/>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G97" s="3" t="inlineStr">
+      <c r="E97" s="7" t="inlineStr"/>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
         <is>
           <t>3001045</t>
         </is>
       </c>
-      <c r="H97" s="3" t="inlineStr">
+      <c r="H97" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -6053,40 +6053,40 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B132" s="3" t="inlineStr">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C132" s="3" t="inlineStr">
+      <c r="C132" s="7" t="inlineStr">
         <is>
           <t>Sun Care Ultra Fluid Ultra-Mat SPF50
 Protetor Solar Fluido Rosto Mat Pele Sensível
 50 ml</t>
         </is>
       </c>
-      <c r="D132" s="3" t="inlineStr">
+      <c r="D132" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/sun-care-ultra-fluid-ultra-mat-spf50-7536015.html</t>
         </is>
       </c>
-      <c r="E132" s="3" t="inlineStr"/>
-      <c r="F132" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G132" s="3" t="inlineStr">
+      <c r="E132" s="7" t="inlineStr"/>
+      <c r="F132" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="inlineStr">
         <is>
           <t>7536015</t>
         </is>
       </c>
-      <c r="H132" s="3" t="inlineStr">
+      <c r="H132" s="7" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -6542,40 +6542,40 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B144" s="3" t="inlineStr">
+      <c r="A144" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C144" s="3" t="inlineStr">
+      <c r="C144" s="7" t="inlineStr">
         <is>
           <t>Vitamin Activ Cg Eco-Refill Radiance Cream
 Recarga Creme Rugas Vitamina C
 50 ml</t>
         </is>
       </c>
-      <c r="D144" s="3" t="inlineStr">
+      <c r="D144" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/vitamin-activ-cg-eco-refill-radiance-cream-7982202.html</t>
         </is>
       </c>
-      <c r="E144" s="3" t="inlineStr"/>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G144" s="3" t="inlineStr">
+      <c r="E144" s="7" t="inlineStr"/>
+      <c r="F144" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G144" s="7" t="inlineStr">
         <is>
           <t>7982202</t>
         </is>
       </c>
-      <c r="H144" s="3" t="inlineStr">
+      <c r="H144" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -6702,40 +6702,40 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B148" s="3" t="inlineStr">
+      <c r="A148" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C148" s="3" t="inlineStr">
+      <c r="C148" s="7" t="inlineStr">
         <is>
           <t>Xeracalm A.D Lipid-Replenishing Balm
 Bálsamo Relipidante Pele Seca Atópica Comichão
 200 ml</t>
         </is>
       </c>
-      <c r="D148" s="3" t="inlineStr">
+      <c r="D148" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/xeracalm-a.d-lipid-replenishing-balm-5195068.html</t>
         </is>
       </c>
-      <c r="E148" s="3" t="inlineStr"/>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G148" s="3" t="inlineStr">
+      <c r="E148" s="7" t="inlineStr"/>
+      <c r="F148" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G148" s="7" t="inlineStr">
         <is>
           <t>5195068</t>
         </is>
       </c>
-      <c r="H148" s="3" t="inlineStr">
+      <c r="H148" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -6822,40 +6822,40 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="5" t="inlineStr">
+      <c r="A151" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C151" s="5" t="inlineStr">
+      <c r="C151" s="7" t="inlineStr">
         <is>
           <t>Xeracalm A.D Lipid-Replenishing Cleansing Oil
 Óleo de Limpeza Pele Seca Atópica Comichão
 750 ml</t>
         </is>
       </c>
-      <c r="D151" s="5" t="inlineStr">
+      <c r="D151" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/xeracalm-a.d-lipid-replenishing-cleansing-oil-7889347.html</t>
         </is>
       </c>
-      <c r="E151" s="5" t="inlineStr"/>
-      <c r="F151" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G151" s="5" t="inlineStr">
+      <c r="E151" s="7" t="inlineStr"/>
+      <c r="F151" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="inlineStr">
         <is>
           <t>7889347</t>
         </is>
       </c>
-      <c r="H151" s="5" t="inlineStr">
+      <c r="H151" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -7022,40 +7022,40 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B156" s="3" t="inlineStr">
+      <c r="A156" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C156" s="3" t="inlineStr">
+      <c r="C156" s="7" t="inlineStr">
         <is>
           <t>Xeracalm AD Ultra-Rich Bar
 Sabonete sem sabão Pele Seca Atópica Comichão
 100 gr</t>
         </is>
       </c>
-      <c r="D156" s="3" t="inlineStr">
+      <c r="D156" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/xeracalm-ad-ultra-rich-bar-8429921.html</t>
         </is>
       </c>
-      <c r="E156" s="3" t="inlineStr"/>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G156" s="3" t="inlineStr">
+      <c r="E156" s="7" t="inlineStr"/>
+      <c r="F156" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G156" s="7" t="inlineStr">
         <is>
           <t>8429921</t>
         </is>
       </c>
-      <c r="H156" s="3" t="inlineStr">
+      <c r="H156" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -7589,414 +7589,414 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
+          <t>Bálsamo Emoliente Antiprurido Dexyane
+Bálsamo Antiprurido Pele Seca e Eczema Atópico
+400 ml</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/balsamo-emoliente-antiprurido-dexyane-5976214.html</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>5976214</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Ducray</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
           <t>Cápsulas Queda Cabelo Crónica Anacaps Expert
 Suplemento Alimentar Queda de Cabelo Crónica
 90 cápsulas</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/capsulas-queda-cabelo-cronica-anacaps-expert-7786545.html</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>7786545</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Creme de Noite Antimanchas Melascreen
+Creme de Rosto Noite Antimanchas
+50 ml</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/creme-de-noite-antimanchas-melascreen-6136887.html</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>6136887</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Ducray</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Creme Emoliente Antiprurido Dexyane
+Creme Antiprurido Pele Seca e Eczema Atópico
+400 ml</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/creme-emoliente-antiprurido-dexyane-5976217.html</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>5976217</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Ducray</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Creme Palpebral Eczema Dexyane Med
 Creme Eczema da Pálpebra
 15 ml</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/creme-palpebral-eczema-dexyane-med-7024952.html</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>7024952</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Creme Rosto Anti Imperfeições Keracnyl SPF50
 Fluido Anti-imperfeições Oleosa Acne SPF50+
 50 ml</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/creme-rosto-anti-imperfeicoes-keracnyl-spf50-7607779.html</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>7607779</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Creme Rosto Dermatite Seborreica Kelual DS
 Creme Redução Pele Descamada e Vermelhidão
 40 ml</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/creme-rosto-dermatite-seborreica-kelual-ds-4028956.html</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>4028956</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Creme Tratamento do Eczema Dexyane 30ml
 Creme Reparador Trata Lesões de Eczema
 30 ml</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/creme-tratamento-do-eczema-dexyane-30ml-5976172.html</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>5976172</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Creme Tratamento do Eczema Dexyane
 Creme Reparador Trata Lesões de Eczema
 100 ml</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/creme-tratamento-do-eczema-dexyane-5976178.html</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>5976178</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Dexyane Anti-Scratching Emollient Balm
 Bálsamo Rosto Corpo Pele Seca Eczema e Atópica
 200 ml</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/dexyane-anti-scratching-emollient-balm-5976179.html</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>5976179</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Dexyane Anti-Scratching Emollient Balm
-Bálsamo Antiprurido Pele Seca e Eczema Atópico
-400 ml</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>https://wells.pt/dexyane-anti-scratching-emollient-balm-5976214.html</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>5976214</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Ducray</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Dexyane Anti-Scratching Emollient Cream
 Creme Rosto Corpo Pele Seca Eczema e Atópica
 200 ml</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/dexyane-anti-scratching-emollient-cream-5976215.html</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>5976215</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Ducray</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Dexyane Anti-Scratching Emollient Cream
-Creme Antiprurido Pele Seca e Eczema Atópico
-400 ml</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>https://wells.pt/dexyane-anti-scratching-emollient-cream-5976217.html</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>5976217</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Ducray</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Dexyane Ultra-Rich Cleansing Gel
-Gel de Limpeza Calmante Pele Seca e Atópica
-400 ml</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>https://wells.pt/dexyane-ultra-rich-cleansing-gel-5976219.html</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr"/>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>5976219</t>
+          <t>5976215</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -8361,1148 +8361,1148 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
+          <t>Gel de Limpeza Pele Seca e Atópica Dexyane
+Gel de Limpeza Calmante Pele Seca e Atópica
+400 ml</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/gel-de-limpeza-pele-seca-e-atopica-dexyane-5976219.html</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>5976219</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Ducray</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
           <t>Gel Rubéfiant Tonique Capillaire
 Gel Rubefaciente Queda Cabelo Alopécia Pelada
 30 ml</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/gel-rubefiant-tonique-capillaire-3691734.html</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>3691734</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Kelual DS Gel Nettoyant Anti-squames
 Gel Limpeza Dermatite Seborreica
 200 ml</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/kelual-ds-gel-nettoyant-anti-squames-8226845.html</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>8226845</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Kelual DS Intensive Anti-Dandruff Shampoo
 Champô Tratamento Caspa Anti-comichão
 100 ml</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/kelual-ds-intensive-anti-dandruff-shampoo-8542652.html</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>8542652</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Kelual DS Sensinol Spray SOS
 Spray Couro Cabeludo Calmante Anti-comichão
 30 ml</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/kelual-ds-sensinol-spray-sos-8199454.html</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>8199454</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>Kelual DS Treatment Shampoo
 Champô Calmante Comichão Elimina a Caspa
 100 ml</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/kelual-ds-treatment-shampoo-3600258.html</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>3600258</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>Kelual Squanorm Anti-Dandruff Refresh Lotion
 Loção Leave-in Refrescante Cabelo com Caspa
 190 ml</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/kelual-squanorm-anti-dandruff-refresh-lotion-8660190.html</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr"/>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr"/>
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="G34" s="7" t="inlineStr">
         <is>
           <t>8660190</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>Kelual Squanorm Anti-Dandruff Refreshing
 Champô Resfrescante Cabelo com Caspa
 400 ml</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/kelual-squanorm-anti-dandruff-refreshing-8660180.html</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr"/>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>8660180</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>Kelual Squanorm Anti-Dandruff Refreshing
 Champô Resfrescante Cabelo com Caspa
 200 ml</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/kelual-squanorm-anti-dandruff-refreshing-8710845.html</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr"/>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr"/>
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>8710845</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>Kelual Squanorm Moisturizing Treatment Shampoo
 Champô Hidratante Caspa Seca</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/kelual-squanorm-moisturizing-treatment-shampoo-374577.html</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>400 ml</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>8197119</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>Kelual Squanorm Moisturizing Treatment Shampoo
 Champô Hidratante Caspa Seca</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/kelual-squanorm-moisturizing-treatment-shampoo-374577.html</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>8197145</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Kelual Squanorm Regulating Treatment Shampoo
 Champô Caspa Oleosa
 1 un</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/kelual-squanorm-regulating-treatment-shampoo-374576.html</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>8196985</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>Kelual Squanorm Regulating Treatment Shampoo
 Champô Caspa Oleosa
 1 un</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/kelual-squanorm-regulating-treatment-shampoo-374576.html</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>400 ml</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>8196986</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>Keracnyl Anti-blemishes Regulating Serum
 Sérum Anti-Imperfeições Sebo-Regulador Acne
 30 ml</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/keracnyl-anti-blemishes-regulating-serum-8539819.html</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr"/>
-      <c r="F40" s="8" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr"/>
+      <c r="F41" s="8" t="inlineStr">
         <is>
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>8539819</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>Keracnyl Cleansing Gel Anti-Imperfections
 Gel Limpeza de Rosto e Corpo Pele Acneia
 200 ml</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/keracnyl-cleansing-gel-anti-imperfections-3601978.html</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr"/>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>3601978</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>Keracnyl Gel Moussant Visage &amp; Corps
 Gel Limpeza Purificante Pele Oleosa com Acne
 400 ml</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/keracnyl-gel-moussant-visage-and-corps-6606365.html</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr"/>
-      <c r="F42" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr"/>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>6606365</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>Keracnyl Glycolic+ Crème Desincrustante
 Creme Redutor Borbulhas Acne e Pontos Negros
 30ml</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/keracnyl-glycolic-creme-desincrustante-7453182.html</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr"/>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>7453182</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>Keracnyl Lotion Purifiante
 Loção Purificante Acne Matifica e Fecha Poros
 200 ml</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/keracnyl-lotion-purifiante-3891879.html</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr"/>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>3891879</t>
         </is>
       </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>Keracnyl Mat 12H Oily Skin
 Gel Matificante Pele Oleosa Ação Anti-brilho
 30 ml</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/keracnyl-mat-12h-oily-skin-6037944.html</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr"/>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
         <is>
           <t>6037944</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>Keracnyl PP+ Crème Anti-imperfections
 Creme Anti-Imperfeições e Marcas Pele Acneica
 30ml</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/keracnyl-pp-creme-anti-imperfections-7453185.html</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr"/>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>7453185</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>Keracnyl Repair Baume Lèvres
 Bálsamo Lábios Gretados e Danificados Acne
 15 ml</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/keracnyl-repair-baume-levres-5410512.html</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr"/>
-      <c r="F47" s="8" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr"/>
+      <c r="F48" s="8" t="inlineStr">
         <is>
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>5410512</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>Keracnyl Repair Crème 48h D'Hydratation
 Creme Compensador de Tratamento de Acne
 50 ml</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/keracnyl-repair-creme-48h-dhydratation-5410519.html</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr"/>
-      <c r="F48" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>5410519</t>
         </is>
       </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>Keracnyl Stop Care Drying Gel
 Gel SOS Localizado Stop Acne e Borbulhas
 10 ml</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/keracnyl-stop-care-drying-gel-3601988.html</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr"/>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>3601988</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>Kertyol PSO Cleansing Gel
 Gel de Limpeza Rosto Ultra Rico Pele Psoríase
 400 ml</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/kertyol-pso-cleansing-gel-8487441.html</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr"/>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>8487441</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>Kertyol PSO Daily Balm
 Bálsamo Corpo Hidratante Pele com Psoríase
 200 ml</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/kertyol-pso-daily-balm-8487355.html</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr"/>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr"/>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>8487355</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="H52" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>Kertyol PSO Daily Balm
 Bálsamo Corpo Hidratante Pele com Psoríase
 400 ml</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/kertyol-pso-daily-balm-8487356.html</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr"/>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>8487356</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>Kertyol PSO Shampooing Traitant
 Champô para Pele com Tendência a Psoríase
 200 ml</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/kertyol-pso-shampooing-traitant-3069435.html</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr"/>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr"/>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>3069435</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>Kit Anaphase Anti-Hair Loss and Growth
 Champô Queda de Cabelo Reativa com Oferta
 1 un</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/kit-anaphase-anti-hair-loss-and-growth-8640386.html</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr"/>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>8640386</t>
         </is>
       </c>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr">
         <is>
           <t>Sem desconto</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>Ducray</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>Melascreen Anti-spots concentrate Brown Spots
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Melascreen Concentré Antitaches Brunes
 Creme Rosto Concentrado Antimanchas
 30 ml</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>https://wells.pt/melascreen-anti-spots-concentrate-brown-spots-7850405.html</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr"/>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>7850405</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>Ducray</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>Melascreen Anti-spots Radiance Serum
-Sérum de Rosto Iluminador Antimanchas
-40 ml</t>
-        </is>
-      </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>https://wells.pt/melascreen-anti-spots-radiance-serum-7850440.html</t>
+          <t>https://wells.pt/melascreen-concentre-antitaches-brunes-7850405.html</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr"/>
@@ -9513,7 +9513,7 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>7850440</t>
+          <t>7850405</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
@@ -9655,14 +9655,14 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Melascreen Photo-aging Night Cream
-Creme de Rosto Noite Antimanchas
-50 ml</t>
+          <t>Melascreen Sérum Antitaches Éclat
+Sérum de Rosto Iluminador Antimanchas
+40 ml</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>https://wells.pt/melascreen-photo-aging-night-cream-6136887.html</t>
+          <t>https://wells.pt/melascreen-serum-antitaches-eclat-7850440.html</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr"/>
@@ -9673,7 +9673,7 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>6136887</t>
+          <t>7850440</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
@@ -10250,2753 +10250,2753 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Avoine Extra-Doux Shampoo
-Champô Aveia Ultra-Suave Cabelo Norma</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>https://wells.pt/avoine-extra-doux-shampoo-343978.html</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>400 ml</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>3000705</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Klorane</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Avoine Extra-Doux Shampoo
-Champô Aveia Ultra-Suave Cabelo Norma</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>https://wells.pt/avoine-extra-doux-shampoo-343978.html</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>200 ml</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>3000709</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Klorane</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Avoine Extra-Doux Shampoo
-Champô Aveia Ultra-Suave Cabelo Norma</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>https://wells.pt/avoine-extra-doux-shampoo-343978.html</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>100 ml</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>3809464</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Klorane</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
           <t>Bebé Cleansing Lotion No-Rise
 Leite Limpeza Fralda e Mãos 0 meses
 500 ml</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/bebe-cleansing-lotion-no-rise-6661598.html</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>6661598</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Bebé Cleansing Water
 Água de Limpeza Hidratante Bebé
 400 ml</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/bebe-cleansing-water-8564071.html</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr"/>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>8564071</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Sem desconto</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Bebé Detangling Shampoo
 Champô Suave a partir de 0 meses
 200 ml</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/bebe-detangling-shampoo-6661442.html</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>6661442</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Bebé Moisturing Cream BIO
 Creme Hidratante Rosto e Corpo 0 meses
 200 ml</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/bebe-moisturing-cream-bio-7831744.html</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>7831744</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Bebé Multi-Purpose Oil BIO
 Óleo Multiusos BIO Limpa Nutre desde 0 meses
 200 ml</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/bebe-multi-purpose-oil-bio-7831747.html</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>7831747</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Bebé Nappy Cream BIO
 Creme Muda da Fralda 0 meses
 100 ml</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/bebe-nappy-cream-bio-7831740.html</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>7831740</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Bebé Nourishing Cream With Cold Cream
 Creme Nutritivo Pele Seca 0 meses
 125 ml</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/bebe-nourishing-cream-with-cold-cream-6661554.html</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>6661554</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Bebé Refreshing Scented Water
 Água Perfumada Cabelo pele Normal 0 meses
 500 ml</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/bebe-refreshing-scented-water-6935360.html</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>6935360</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Centaury Anti-Yellowing Gray, Blond Shampoo
 Champô Centáurea BIO Neutraliza Tons Amarelos
 400 ml</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/centaury-anti-yellowing-gray-blond-shampoo-6863851.html</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>6863851</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>Centaury Anti-Yellowing Neutral Conditioner
 Condicionador CentáureaBIO Neutraliza Amarelo
 200 ml</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/centaury-anti-yellowing-neutral-conditioner-7447294.html</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr"/>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>7447294</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Chamomile Brightening Blond Hair Conditioner
 Condicionador Camomila Brilho Cabelo Loiro
 200 ml</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/chamomile-brightening-blond-hair-conditioner-5870419.html</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>5870419</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Chamomile Brightening Blond Hair Shampoo
 Champô Camomila Reflexos Dourado Cabelo Loiro</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/chamomile-brightening-blond-hair-shampoo-343981.html</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>3000697</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Chamomile Brightening Blond Hair Shampoo
 Champô Camomila Reflexos Dourado Cabelo Loiro</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/chamomile-brightening-blond-hair-shampoo-343981.html</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>400 ml</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>3000699</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>Chamomile Brightening Blond Hair Spray
 Spray Camomila Aclarador 3-em-1 Cabelo Loiro
 100 ml</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/chamomile-brightening-blond-hair-spray-7615327.html</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr"/>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr"/>
+      <c r="F15" s="8" t="inlineStr">
         <is>
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>7615327</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Citrus Purifying Normal to Oily Hair Shampoo
 Champô Cidra BIO Purifica Cabelo Oleoso
 200 ml</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/citrus-purifying-normal-to-oily-hair-shampoo-3066199.html</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>3066199</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Citrus Purifying Normal to Oily Hair Shampoo
 Champô Cidra BIO Purifica Cabelo Oleoso
 400 ml</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/citrus-purifying-normal-to-oily-hair-shampoo-3066206.html</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>3066206</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Crème Solaire Sublime SPF 30
 Protetor Solar de Rosto Antienvelhecimento
 50 ml</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/creme-solaire-sublime-spf-30-7129218.html</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>7129218</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Crème Solaire Sublime SPF 50+
 Protetor Solar de Rosto Antienvelhecimento
 50 ml</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/creme-solaire-sublime-spf-50-7129219.html</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>7129219</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Crème Sublimatrice Après-Soleil
 Creme Pós Solar Reparador Nutritivo
 200 ml</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/creme-sublimatrice-apres-soleil-7129225.html</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr"/>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr"/>
+      <c r="F20" s="8" t="inlineStr">
         <is>
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>7129225</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Cupuaçu BIO Creme Duche Nutri Frangipanier
 Creme Duche Hidratante e Nutritivo Frangipani
 200 ml</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/cupuacu-bio-creme-duche-nutri-frangipanier-7724349.html</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>7724349</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Cupuaçu BIO Creme Duche Nutritivo
 Creme Duche Hidratante e Nutritivo Cupuaçu
 200 ml</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/cupuacu-bio-creme-duche-nutritivo-6515197.html</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>6515197</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Cupuaçu BIO Creme Duche Nutritivo Amandier
 Creme Duche Hidratante Leite Amêndoa
 200 ml</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/cupuacu-bio-creme-duche-nutritivo-amandier-7724346.html</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>7724346</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Cupuaçu BIO Gel Duche Nutritivo Cèdre
 Gel Duche Hidratante e Nutritivo Cedro
 200 ml</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/cupuacu-bio-gel-duche-nutritivo-cedre-7724348.html</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>7724348</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Cupuaçu BIO Gel Duche Nutritivo Fève de Tonka
 Gel Duche Hidratante e Nutritivo Fava Tonka
 200 ml</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/cupuacu-bio-gel-duche-nutritivo-feve-de-tonka-7724352.html</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>7724352</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Cupuaçu BIO Gel Duche Nutritivo Figuier
 Gel Duche Hidratante e Nutritivo Figueira
 200 ml</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/cupuacu-bio-gel-duche-nutritivo-figuier-7724345.html</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>7724345</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Cupuaçu BIO Gel Duche Nutritivo Hibiscus
 Gel Duche Hidratante Flor de Hibísco
 200 ml</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/cupuacu-bio-gel-duche-nutritivo-hibiscus-6515228.html</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>6515228</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Cupuaçu Repairing CICA-shampoo
 Champô Cupuaçu Nutre Repara Cabelo Muito Seco
 200 ml</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/cupuacu-repairing-cica-shampoo-8500174.html</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>8500174</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>Cupuaçu Repairing Conditioner
 Condicionador Cupuaçu Nutre Repara Cabelo Seco
 200 ml</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/cupuacu-repairing-conditioner-8500259.html</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>8500259</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Cupuaçu Repairing Restorative CICA-Serum
 Sérum Cupuaçu Repara Cabelo Muito Seco
 100 ml</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/cupuacu-repairing-restorative-cica-serum-8557935.html</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>8557935</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Cupuaçu Reparing Very Dry Hair Shampoo
 Champô Cupuaçu BIO Repara Cabelo Muito Seco
 400 ml</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/cupuacu-reparing-very-dry-hair-shampoo-343983.html</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr"/>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>7104602</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Eau de Parfumee e Oferta de Coelho
 1 un</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/eau-de-parfumee-e-oferta-de-coelho-6661579.html</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>6661579</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>Flax Volume Fine Hair Conditioner
 Condicionador Linho BIO Volume Cabelo Fino
 200 ml</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/flax-volume-fine-hair-conditioner-5924193.html</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr"/>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>5924193</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Flax Volume Fine Hair Shampoo
 Champô Fibras de Linho BIO Volume Cabelo Fino</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/flax-volume-fine-hair-shampoo-343984.html</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>5221797</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Flax Volume Fine Hair Shampoo
 Champô Fibras de Linho BIO Volume Cabelo Fino</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/flax-volume-fine-hair-shampoo-343984.html</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>400 ml</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>5418515</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>Galanga Anti-Dandruff Anti-itching Treatment
 Loção Anti Caspa Tratamento Anti-comichão
 100 ml</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/galanga-anti-dandruff-anti-itching-treatment-8544717.html</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr"/>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>8544717</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Galanga Anti-Dandruff Shampoo
 Champô Anti Caspa Reequilibra e Trata</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/galanga-anti-dandruff-shampoo-427225.html</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>8544713</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>Galanga Anti-Dandruff Shampoo
 Champô Anti Caspa Reequilibra e Trata</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/galanga-anti-dandruff-shampoo-427225.html</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>400 ml</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>8544715</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>Galanga Treating Powder-Mask Dandruff
 Máscara Galanga Pó elimina Caspa Persistente
 8x3 gr</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/galanga-treating-powder-mask-dandruff-7610893.html</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr"/>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr"/>
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G42" s="7" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>7610893</t>
         </is>
       </c>
-      <c r="H42" s="7" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>Gel-Crème Solaire Sublime SPF 30
 Protetor Solar de Corpo Nutritivo
 200 ml</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/gel-creme-solaire-sublime-spf-30-7129220.html</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr"/>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>7129220</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>Gel Lavante Suave Bebé
 500 ml</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/gel-lavante-suave-bebe-6661468.html</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr"/>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>6661468</t>
         </is>
       </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>Grenade Éclat Couleur Shampooing
 Champô Iluminador e Potenciador de Cor</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/grenade-eclat-couleur-shampooing-3688252.html</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr"/>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>3688252</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>Hair Removal Cream Sweet Almond
 Creme Depilatório pele Sensível Amêndoas Doce
 150 ml</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/hair-removal-cream-sweet-almond-7724355.html</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr"/>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>7724355</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>Huile Réparatrice Après-Soleil
 Óleo Protetor de Cabelo Nutritivo
 150 ml</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/huile-reparatrice-apres-soleil-7546027.html</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr"/>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>7546027</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>Huile Sèche Solaire SPF 30
 Protetor Solar de Corpo e Cabelo
 200 ml</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/huile-seche-solaire-spf-30-7129222.html</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr"/>
-      <c r="F48" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>7129222</t>
         </is>
       </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>Junior 2-in-1 Shower Gel Pear
 Gel Duche Pêra Corpo e Cabelo 3 anos
 200 ml</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/junior-2-in-1-shower-gel-pear-3037963.html</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr"/>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>3037963</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>Junior Detangling Shampoo
 Champô de Pêssego a partir de 3 anos
 500 ml</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/junior-detangling-shampoo-3066288.html</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr"/>
-      <c r="F50" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>3066288</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>Keratincaps Força e Vitalidade Cabelo e Unhas
 Via Oral Cápsula Keratina Queda de Cabelo
 30 cápsulas</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/keratincaps-forca-e-vitalidade-cabelo-e-unhas-6283642.html</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr"/>
-      <c r="F51" s="8" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr"/>
+      <c r="F48" s="8" t="inlineStr">
         <is>
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>6283642</t>
         </is>
       </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>Leite Hidratante Bebé
 500 ml</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/leite-hidratante-bebe-6661555.html</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr"/>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>6661555</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>Mango Nourishing Conditioner
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Manga Nourishing Conditioner
 Condicionador Manga Nutritivo Cabelo Seco</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>https://wells.pt/mango-nourishing-conditioner-343975.html</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/manga-nourishing-conditioner-343975.html</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>200 ml</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>5924180</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Klorane</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Manga Nourishing Conditioner
+Condicionador Manga Nutritivo Cabelo Seco</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/manga-nourishing-conditioner-343975.html</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>50 ml</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>6128332</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>Mango Nourishing Conditioner
-Condicionador Manga Nutritivo Cabelo Seco</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>https://wells.pt/mango-nourishing-conditioner-343975.html</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>200 ml</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>5924180</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>Klorane</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>Mango Nourishing Leave-In Cream
 Creme Dia Manga Nutritivo SOS Cabelo Seco
 125ml</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/mango-nourishing-leave-in-cream-5072223.html</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr"/>
-      <c r="F55" s="8" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr"/>
+      <c r="F52" s="8" t="inlineStr">
         <is>
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G55" s="7" t="inlineStr">
+      <c r="G52" s="7" t="inlineStr">
         <is>
           <t>5072223</t>
         </is>
       </c>
-      <c r="H55" s="7" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>Mango Nourishing Mask
 Máscara Manga Nutritiva Hidrata Cabelo Seco
 150 ml</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/mango-nourishing-mask-3066267.html</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr"/>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr"/>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>3066267</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>Mango Nourishing Shampoo
 Champô Manga Nutritivo para Cabelo Seco</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/mango-nourishing-shampoo-344278.html</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="F57" s="8" t="inlineStr">
+      <c r="F54" s="8" t="inlineStr">
         <is>
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G57" s="7" t="inlineStr">
+      <c r="G54" s="7" t="inlineStr">
         <is>
           <t>3018059</t>
         </is>
       </c>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>Mango Nourishing Shampoo
 Champô Manga Nutritivo para Cabelo Seco</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/mango-nourishing-shampoo-344278.html</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>400 ml</t>
         </is>
       </c>
-      <c r="F58" s="8" t="inlineStr">
+      <c r="F55" s="8" t="inlineStr">
         <is>
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G58" s="7" t="inlineStr">
+      <c r="G55" s="7" t="inlineStr">
         <is>
           <t>3066184</t>
         </is>
       </c>
-      <c r="H58" s="7" t="inlineStr">
+      <c r="H55" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>Mango Nourishing Shampoo
 Champô Manga Nutritivo para Cabelo Seco</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/mango-nourishing-shampoo-344278.html</t>
         </is>
       </c>
-      <c r="E59" s="7" t="inlineStr">
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>100 ml</t>
         </is>
       </c>
-      <c r="F59" s="8" t="inlineStr">
+      <c r="F56" s="8" t="inlineStr">
         <is>
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G59" s="7" t="inlineStr">
+      <c r="G56" s="7" t="inlineStr">
         <is>
           <t>6128309</t>
         </is>
       </c>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>Mango Nutrition Oil
 Óleo de Manga Nutritivo Cabelo Seco
 125 ml</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/mango-nutrition-oil-7369351.html</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr"/>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr"/>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>7369351</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>Nettle &amp; Clay 2-in-1 Mask Shampoo
 Máscara Champô Pó Ortiga BIO Cabelo Oleoso
 150 ml</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/nettle-and-clay-2-in-1-mask-shampoo-7339155.html</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr"/>
-      <c r="F61" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
         <is>
           <t>7339155</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr">
+      <c r="H58" s="3" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>Nettle &amp; Vitamin E Oil Control Dry Shampoo
 Champô Seco Ortiga BIO Cabelo Oleoso</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/nettle-and-vitamin-e-oil-control-dry-shampoo-366180.html</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>50 ml</t>
         </is>
       </c>
-      <c r="F62" s="8" t="inlineStr">
+      <c r="F59" s="8" t="inlineStr">
         <is>
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G62" s="7" t="inlineStr">
+      <c r="G59" s="7" t="inlineStr">
         <is>
           <t>8123735</t>
         </is>
       </c>
-      <c r="H62" s="7" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>Nettle &amp; Vitamin E Oil Control Dry Shampoo
 Champô Seco Ortiga BIO Cabelo Oleoso</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/nettle-and-vitamin-e-oil-control-dry-shampoo-366180.html</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>150 ml</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>8123759</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>Nettle &amp; Vitamin E Oil Control Dry Shampoo
 Champô Seco Ortiga BIO Cabelo Oleoso Castanho
 150 ml</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/nettle-and-vitamin-e-oil-control-dry-shampoo-8123760.html</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr"/>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr"/>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t>8123760</t>
         </is>
       </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>Nettle Oil Control Shampoo
 Champô Ortiga BIO Purifica Cabelo Oleoso</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/nettle-oil-control-shampoo-343980.html</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
+      <c r="E62" s="7" t="inlineStr">
         <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="F65" s="8" t="inlineStr">
+      <c r="F62" s="8" t="inlineStr">
         <is>
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="G65" s="7" t="inlineStr">
+      <c r="G62" s="7" t="inlineStr">
         <is>
           <t>3000693</t>
         </is>
       </c>
-      <c r="H65" s="7" t="inlineStr">
+      <c r="H62" s="7" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>Nettle Oil Control Shampoo
 Champô Ortiga BIO Purifica Cabelo Oleoso</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/nettle-oil-control-shampoo-343980.html</t>
         </is>
       </c>
-      <c r="E66" s="3" t="inlineStr">
+      <c r="E63" s="5" t="inlineStr">
         <is>
           <t>400 ml</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
         <is>
           <t>3688262</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
+      <c r="H63" s="5" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>Oat &amp; Ceramide Ultra-Gentle Dry Shampoo
 Champô Seco Aveia Spray Suave Cabelo Normal</t>
         </is>
       </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/oat-and-ceramide-ultra-gentle-dry-shampoo-341981.html</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>50 ml</t>
         </is>
       </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
         <is>
           <t>7831152</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>Oat &amp; Ceramide Ultra-Gentle Dry Shampoo
 Champô Seco Aveia Spray Suave Cabelo Normal</t>
         </is>
       </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>https://wells.pt/oat-and-ceramide-ultra-gentle-dry-shampoo-341981.html</t>
         </is>
       </c>
-      <c r="E68" s="5" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>150 ml</t>
         </is>
       </c>
-      <c r="F68" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G68" s="5" t="inlineStr">
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>7831153</t>
         </is>
       </c>
-      <c r="H68" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>Oat Ultra-Gentle All HairTypes Conditioner
 Condicionador Aveia Suave e Protetor
 200 ml</t>
         </is>
       </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/oat-ultra-gentle-all-hairtypes-conditioner-5924188.html</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr"/>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>5924188</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Klorane</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Oat Ultra-Gentle All HairTypes Shampoo
+Champô Aveia Ultra-Suave Cabelo Norma</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/oat-ultra-gentle-all-hairtypes-shampoo-343978.html</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>400 ml</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>3000705</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Klorane</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Oat Ultra-Gentle All HairTypes Shampoo
+Champô Aveia Ultra-Suave Cabelo Norma</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/oat-ultra-gentle-all-hairtypes-shampoo-343978.html</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>200 ml</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>3000709</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Klorane</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Oat Ultra-Gentle All HairTypes Shampoo
+Champô Aveia Ultra-Suave Cabelo Norma</t>
+        </is>
+      </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>https://wells.pt/oat-ultra-gentle-all-hairtypes-conditioner-5924188.html</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr"/>
+          <t>https://wells.pt/oat-ultra-gentle-all-hairtypes-shampoo-343978.html</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>100 ml</t>
+        </is>
+      </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
           <t>In Stock</t>
@@ -13004,12 +13004,12 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>5924188</t>
+          <t>3809464</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
@@ -13708,7 +13708,7 @@
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>3000714</t>
+          <t>3000716</t>
         </is>
       </c>
       <c r="H86" s="5" t="inlineStr">
@@ -13751,12 +13751,12 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>3000714</t>
+          <t>4468119</t>
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>35%</t>
         </is>
       </c>
     </row>
@@ -13881,40 +13881,40 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C91" s="7" t="inlineStr">
         <is>
           <t>Tamanu &amp; Monoi Nutri-Repair Sun Conditioner
 Condicionador Protetor Solar para Cabelo
 200 ml</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D91" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/tamanu-and-monoi-nutri-repair-sun-conditioner-7396247.html</t>
         </is>
       </c>
-      <c r="E91" s="5" t="inlineStr"/>
-      <c r="F91" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="inlineStr">
+      <c r="E91" s="7" t="inlineStr"/>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
         <is>
           <t>7396247</t>
         </is>
       </c>
-      <c r="H91" s="5" t="inlineStr">
+      <c r="H91" s="7" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
@@ -17986,43 +17986,43 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>A-Derma</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Epitheliale Ultra Repair Cream SPF50+
 Creme Protetor Solar Reparador</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/epitheliale-ultra-repair-cream-spf50-412214.html</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>40 ml</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>8478836</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -18189,43 +18189,43 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>A-Derma</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>Exomega Allergo Emollient Balm
 Bálsamo Nutritivo Pele Atópica Alérgica</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/exomega-allergo-emollient-balm-452820.html</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>40 ml</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
         <is>
           <t>7631532</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -18401,43 +18401,43 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>A-Derma</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Exomega Control Emolient Shower Oil
 Óleo Banho Calmante Comichão da Pele Atópica</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/exomega-control-emolient-shower-oil-452817.html</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>500 ml</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>6587176</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
@@ -18487,43 +18487,43 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>A-Derma</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>Exomega Control Emolient Shower Oil
 Óleo Banho Calmante Comichão da Pele Atópica</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/exomega-control-emolient-shower-oil-452817.html</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>1000 ml</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>8605683</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -19714,40 +19714,40 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>A-Derma</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>Ultra-rich Shower Gel 3in1
 Gel Duche Nutritivo e Calmante Pele Seca
 750 ml</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/ultra-rich-shower-gel-3in1-6037067.html</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr"/>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
+      <c r="E61" s="7" t="inlineStr"/>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
         <is>
           <t>6037067</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
+      <c r="H61" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -22848,7 +22848,10 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Ooops! A página que procura não existe…</t>
+          <t>Jean Paul Gaultier
+Le Male in Blue Eau de Parfum
+Perfume para Homem Edição Limitada
+125 ml</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -22862,10 +22865,14 @@
           <t>In Stock</t>
         </is>
       </c>
-      <c r="G77" s="5" t="inlineStr"/>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>8758496</t>
+        </is>
+      </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
-          <t>Sem desconto</t>
+          <t>42%</t>
         </is>
       </c>
     </row>
@@ -24187,7 +24194,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>1000 ml</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -24197,7 +24204,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>8691147</t>
+          <t>8691146</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -24230,7 +24237,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>1000 ml</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -24240,7 +24247,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>8691146</t>
+          <t>8691147</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -24940,38 +24947,38 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>A-Derma</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Epitheliale Ultra Repair Cream SPF50+
 Creme Protetor Solar Reparador</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>40 ml</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>8478836</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/epitheliale-ultra-repair-cream-spf50-412214.html</t>
         </is>
@@ -25016,38 +25023,38 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>A-Derma</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Exomega Allergo Emollient Balm
 Bálsamo Nutritivo Pele Atópica Alérgica</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>40 ml</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>7631532</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/exomega-allergo-emollient-balm-452820.html</t>
         </is>
@@ -25130,38 +25137,38 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>A-Derma</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Exomega Control Emolient Shower Oil
 Óleo Banho Calmante Comichão da Pele Atópica</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>1000 ml</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>8605683</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/exomega-control-emolient-shower-oil-452817.html</t>
         </is>
@@ -25206,38 +25213,38 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>A-Derma</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Exomega Control Emolient Shower Oil
 Óleo Banho Calmante Comichão da Pele Atópica</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>500 ml</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>6587176</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/exomega-control-emolient-shower-oil-452817.html</t>
         </is>
@@ -26730,13 +26737,13 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Avoine Extra-Doux Shampoo
-Champô Aveia Ultra-Suave Cabelo Norma</t>
+          <t>Chamomile Brightening Blond Hair Shampoo
+Champô Camomila Reflexos Dourado Cabelo Loiro</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>100 ml</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -26746,17 +26753,17 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>3809464</t>
+          <t>3000697</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>https://wells.pt/avoine-extra-doux-shampoo-343978.html</t>
+          <t>https://wells.pt/chamomile-brightening-blond-hair-shampoo-343981.html</t>
         </is>
       </c>
     </row>
@@ -26768,71 +26775,71 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Avoine Extra-Doux Shampoo
-Champô Aveia Ultra-Suave Cabelo Norma</t>
+          <t>Chamomile Brightening Blond Hair Shampoo
+Champô Camomila Reflexos Dourado Cabelo Loiro</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
+          <t>400 ml</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>3000699</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/chamomile-brightening-blond-hair-shampoo-343981.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Klorane</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Flax Volume Fine Hair Shampoo
+Champô Fibras de Linho BIO Volume Cabelo Fino</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>3000709</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
-        <is>
-          <t>https://wells.pt/avoine-extra-doux-shampoo-343978.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>Klorane</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>Avoine Extra-Doux Shampoo
-Champô Aveia Ultra-Suave Cabelo Norma</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>400 ml</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>3000705</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>https://wells.pt/avoine-extra-doux-shampoo-343978.html</t>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>5221797</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/flax-volume-fine-hair-shampoo-343984.html</t>
         </is>
       </c>
     </row>
@@ -26844,71 +26851,71 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Chamomile Brightening Blond Hair Shampoo
-Champô Camomila Reflexos Dourado Cabelo Loiro</t>
+          <t>Flax Volume Fine Hair Shampoo
+Champô Fibras de Linho BIO Volume Cabelo Fino</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
+          <t>400 ml</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>5418515</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/flax-volume-fine-hair-shampoo-343984.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Klorane</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Galanga Anti-Dandruff Shampoo
+Champô Anti Caspa Reequilibra e Trata</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>3000697</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>https://wells.pt/chamomile-brightening-blond-hair-shampoo-343981.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>Klorane</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>Chamomile Brightening Blond Hair Shampoo
-Champô Camomila Reflexos Dourado Cabelo Loiro</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>400 ml</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>3000699</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t>https://wells.pt/chamomile-brightening-blond-hair-shampoo-343981.html</t>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>8544713</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/galanga-anti-dandruff-shampoo-427225.html</t>
         </is>
       </c>
     </row>
@@ -26920,71 +26927,71 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Flax Volume Fine Hair Shampoo
-Champô Fibras de Linho BIO Volume Cabelo Fino</t>
+          <t>Galanga Anti-Dandruff Shampoo
+Champô Anti Caspa Reequilibra e Trata</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
+          <t>400 ml</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>8544715</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/galanga-anti-dandruff-shampoo-427225.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Klorane</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Manga Nourishing Conditioner
+Condicionador Manga Nutritivo Cabelo Seco</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
           <t>200 ml</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>5221797</t>
-        </is>
-      </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>https://wells.pt/flax-volume-fine-hair-shampoo-343984.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>Klorane</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>Flax Volume Fine Hair Shampoo
-Champô Fibras de Linho BIO Volume Cabelo Fino</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>400 ml</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>5418515</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>https://wells.pt/flax-volume-fine-hair-shampoo-343984.html</t>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>5924180</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/manga-nourishing-conditioner-343975.html</t>
         </is>
       </c>
     </row>
@@ -26996,13 +27003,13 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Galanga Anti-Dandruff Shampoo
-Champô Anti Caspa Reequilibra e Trata</t>
+          <t>Manga Nourishing Conditioner
+Condicionador Manga Nutritivo Cabelo Seco</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>50 ml</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -27012,169 +27019,169 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>8544713</t>
+          <t>6128332</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>https://wells.pt/galanga-anti-dandruff-shampoo-427225.html</t>
+          <t>https://wells.pt/manga-nourishing-conditioner-343975.html</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>Galanga Anti-Dandruff Shampoo
-Champô Anti Caspa Reequilibra e Trata</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>400 ml</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>8544715</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>https://wells.pt/galanga-anti-dandruff-shampoo-427225.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr">
-        <is>
-          <t>Klorane</t>
-        </is>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>Mango Nourishing Conditioner
-Condicionador Manga Nutritivo Cabelo Seco</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>200 ml</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>5924180</t>
-        </is>
-      </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>https://wells.pt/mango-nourishing-conditioner-343975.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>Klorane</t>
-        </is>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>Mango Nourishing Conditioner
-Condicionador Manga Nutritivo Cabelo Seco</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>50 ml</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>6128332</t>
-        </is>
-      </c>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="G66" s="5" t="inlineStr">
-        <is>
-          <t>https://wells.pt/mango-nourishing-conditioner-343975.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
-          <t>Klorane</t>
-        </is>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>Mango Nourishing Shampoo
 Champô Manga Nutritivo para Cabelo Seco</t>
         </is>
       </c>
-      <c r="C67" s="7" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>100 ml</t>
         </is>
       </c>
-      <c r="D67" s="8" t="inlineStr">
+      <c r="D64" s="8" t="inlineStr">
         <is>
           <t>Out of Stock</t>
         </is>
       </c>
-      <c r="E67" s="7" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>6128309</t>
         </is>
       </c>
-      <c r="F67" s="7" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="G67" s="7" t="inlineStr">
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/mango-nourishing-shampoo-344278.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>Klorane</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>Mango Nourishing Shampoo
+Champô Manga Nutritivo para Cabelo Seco</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>200 ml</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>3018059</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>https://wells.pt/mango-nourishing-shampoo-344278.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>Klorane</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Mango Nourishing Shampoo
+Champô Manga Nutritivo para Cabelo Seco</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>400 ml</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>3066184</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>https://wells.pt/mango-nourishing-shampoo-344278.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Klorane</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Nettle &amp; Vitamin E Oil Control Dry Shampoo
+Champô Seco Ortiga BIO Cabelo Oleoso</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>150 ml</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>8123759</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/nettle-and-vitamin-e-oil-control-dry-shampoo-366180.html</t>
         </is>
       </c>
     </row>
@@ -27186,13 +27193,13 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Mango Nourishing Shampoo
-Champô Manga Nutritivo para Cabelo Seco</t>
+          <t>Nettle &amp; Vitamin E Oil Control Dry Shampoo
+Champô Seco Ortiga BIO Cabelo Oleoso</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>200 ml</t>
+          <t>50 ml</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
@@ -27202,7 +27209,7 @@
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>3018059</t>
+          <t>8123735</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
@@ -27212,7 +27219,7 @@
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>https://wells.pt/mango-nourishing-shampoo-344278.html</t>
+          <t>https://wells.pt/nettle-and-vitamin-e-oil-control-dry-shampoo-366180.html</t>
         </is>
       </c>
     </row>
@@ -27224,13 +27231,13 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Mango Nourishing Shampoo
-Champô Manga Nutritivo para Cabelo Seco</t>
+          <t>Nettle Oil Control Shampoo
+Champô Ortiga BIO Purifica Cabelo Oleoso</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>400 ml</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
@@ -27240,17 +27247,17 @@
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>3066184</t>
+          <t>3000693</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>https://wells.pt/mango-nourishing-shampoo-344278.html</t>
+          <t>https://wells.pt/nettle-oil-control-shampoo-343980.html</t>
         </is>
       </c>
     </row>
@@ -27262,147 +27269,147 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Nettle &amp; Vitamin E Oil Control Dry Shampoo
-Champô Seco Ortiga BIO Cabelo Oleoso</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>150 ml</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>8123759</t>
-        </is>
-      </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="G70" s="5" t="inlineStr">
-        <is>
-          <t>https://wells.pt/nettle-and-vitamin-e-oil-control-dry-shampoo-366180.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="7" t="inlineStr">
-        <is>
-          <t>Klorane</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>Nettle &amp; Vitamin E Oil Control Dry Shampoo
-Champô Seco Ortiga BIO Cabelo Oleoso</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>50 ml</t>
-        </is>
-      </c>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>8123735</t>
-        </is>
-      </c>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="G71" s="7" t="inlineStr">
-        <is>
-          <t>https://wells.pt/nettle-and-vitamin-e-oil-control-dry-shampoo-366180.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="7" t="inlineStr">
-        <is>
-          <t>Klorane</t>
-        </is>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
           <t>Nettle Oil Control Shampoo
 Champô Ortiga BIO Purifica Cabelo Oleoso</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
-        <is>
-          <t>200 ml</t>
-        </is>
-      </c>
-      <c r="D72" s="8" t="inlineStr">
-        <is>
-          <t>Out of Stock</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>3000693</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>400 ml</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>3688262</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="G72" s="7" t="inlineStr">
+      <c r="G70" s="5" t="inlineStr">
         <is>
           <t>https://wells.pt/nettle-oil-control-shampoo-343980.html</t>
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Klorane</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>Oat &amp; Ceramide Ultra-Gentle Dry Shampoo
+Champô Seco Aveia Spray Suave Cabelo Normal</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>150 ml</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>7831153</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/oat-and-ceramide-ultra-gentle-dry-shampoo-341981.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Klorane</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Oat &amp; Ceramide Ultra-Gentle Dry Shampoo
+Champô Seco Aveia Spray Suave Cabelo Normal</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>50 ml</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>7831152</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>https://wells.pt/oat-and-ceramide-ultra-gentle-dry-shampoo-341981.html</t>
+        </is>
+      </c>
+    </row>
     <row r="73">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>Klorane</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>Nettle Oil Control Shampoo
-Champô Ortiga BIO Purifica Cabelo Oleoso</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>400 ml</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>3688262</t>
-        </is>
-      </c>
-      <c r="F73" s="3" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="inlineStr">
-        <is>
-          <t>https://wells.pt/nettle-oil-control-shampoo-343980.html</t>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Oat Ultra-Gentle All HairTypes Shampoo
+Champô Aveia Ultra-Suave Cabelo Norma</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>100 ml</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>3809464</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>https://wells.pt/oat-ultra-gentle-all-hairtypes-shampoo-343978.html</t>
         </is>
       </c>
     </row>
@@ -27414,13 +27421,13 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Oat &amp; Ceramide Ultra-Gentle Dry Shampoo
-Champô Seco Aveia Spray Suave Cabelo Normal</t>
+          <t>Oat Ultra-Gentle All HairTypes Shampoo
+Champô Aveia Ultra-Suave Cabelo Norma</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>150 ml</t>
+          <t>200 ml</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -27430,17 +27437,17 @@
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>7831153</t>
+          <t>3000709</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>https://wells.pt/oat-and-ceramide-ultra-gentle-dry-shampoo-341981.html</t>
+          <t>https://wells.pt/oat-ultra-gentle-all-hairtypes-shampoo-343978.html</t>
         </is>
       </c>
     </row>
@@ -27452,13 +27459,13 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Oat &amp; Ceramide Ultra-Gentle Dry Shampoo
-Champô Seco Aveia Spray Suave Cabelo Normal</t>
+          <t>Oat Ultra-Gentle All HairTypes Shampoo
+Champô Aveia Ultra-Suave Cabelo Norma</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>50 ml</t>
+          <t>400 ml</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -27468,17 +27475,17 @@
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>7831152</t>
+          <t>3000705</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>https://wells.pt/oat-and-ceramide-ultra-gentle-dry-shampoo-341981.html</t>
+          <t>https://wells.pt/oat-ultra-gentle-all-hairtypes-shampoo-343978.html</t>
         </is>
       </c>
     </row>
@@ -27734,12 +27741,12 @@
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>3000714</t>
+          <t>4468119</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -27772,7 +27779,7 @@
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>3000714</t>
+          <t>3000716</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">

--- a/logs/Consolidado_15_03_2026.xlsx
+++ b/logs/Consolidado_15_03_2026.xlsx
@@ -638,10 +638,10 @@
         <v>151</v>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -695,10 +695,10 @@
         <v>71</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
         <v>3</v>
@@ -714,10 +714,10 @@
         <v>47</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -1958,40 +1958,40 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>Avène</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Cleanance Comedomed Peeling Cleansing Gel
 Gel de Limpeza esfoliante pele com Acne
 400 ml</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/cleanance-comedomed-peeling-cleansing-gel-8660052.html</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr"/>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>8660052</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -14862,12 +14862,12 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>6759973</t>
+          <t>7630905</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
@@ -14915,40 +14915,40 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>René Furterer</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>Forticea Strengthening Revitalizing Shampoo
 Champô Fortificante Todos Tipos de Cabelo
 500 ml</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/forticea-strengthening-revitalizing-shampoo-8602496.html</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr"/>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>8602496</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
@@ -17771,43 +17771,43 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>A-Derma</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Dermalibour+ Repairing CICA-Cream
 Creme Reparador Purificante Pele Irritada</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/dermalibour-repairing-cica-cream-452821.html</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>50 ml</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>7434584</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -24795,38 +24795,38 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>A-Derma</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Dermalibour+ Repairing CICA-Cream
 Creme Reparador Purificante Pele Irritada</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>50 ml</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Out of Stock</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>7434584</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>https://wells.pt/dermalibour-repairing-cica-cream-452821.html</t>
         </is>
@@ -27933,12 +27933,12 @@
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>6759973</t>
+          <t>7630905</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
